--- a/inputs/es/LiST countries/BGR_databook.xlsx
+++ b/inputs/es/LiST countries/BGR_databook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B9B6668-E443-451C-A9BD-A2CEA4E771C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{998AE214-7C2D-402B-BAF0-F4201FDBE857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Causas de muerte" sheetId="3" r:id="rId3"/>
     <sheet name="Distribución estado nutricional" sheetId="4" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="5" r:id="rId5"/>
-    <sheet name="Tendencias temporales" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Tendencias temporales" sheetId="6" r:id="rId6"/>
     <sheet name="Pérdida económica" sheetId="7" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="8" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="9" r:id="rId9"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Entradas de población-año base'!$C$47</definedName>
     <definedName name="U5_mortality">'Entradas de población-año base'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -678,8 +678,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -692,8 +691,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -834,35 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -876,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -890,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -917,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -930,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -943,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -956,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -969,35 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1561,8 +1503,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -1732,8 +1673,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1746,8 +1686,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1760,8 +1699,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1774,8 +1712,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2138,8 +2075,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2152,7 +2088,8 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
+Insufficient published research on the intervention’s effect on the outcome.
+Thereofre, set effect of rice = effect of wheat</t>
         </r>
       </text>
     </comment>
@@ -2165,8 +2102,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2192,8 +2128,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2366,8 +2301,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2380,8 +2314,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2394,8 +2327,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2408,8 +2340,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2660,7 +2591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2669,12 +2600,37 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2688,7 +2644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2702,7 +2658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2716,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2730,7 +2686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2744,7 +2700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2758,7 +2714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2772,7 +2728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2786,7 +2742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2800,7 +2756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2814,7 +2770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2828,7 +2784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2856,7 +2812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2870,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2884,7 +2840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2911,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2924,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -2950,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -2963,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -3002,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3011,12 +2967,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3025,12 +2980,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -3039,12 +2993,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -3053,12 +3006,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3086,7 +3038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3100,7 +3052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3114,7 +3066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3142,7 +3094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3156,7 +3108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3170,7 +3122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3184,7 +3136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3198,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3212,7 +3164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3226,7 +3178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3240,7 +3192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3253,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3266,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3279,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3292,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3302,6 +3254,32 @@
           </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -4373,7 +4351,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5023,7 +5001,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5673,7 +5651,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -6941,9 +6919,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6955,9 +6932,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6969,9 +6945,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6983,9 +6958,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7118,68 +7092,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -7192,7 +7110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -7205,7 +7123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -7218,6 +7136,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
@@ -7239,9 +7209,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7253,9 +7222,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7267,9 +7235,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7281,9 +7248,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7370,7 +7336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="341">
   <si>
     <t>Field</t>
   </si>
@@ -9313,7 +9279,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="41">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9322,7 +9288,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="42">
-        <v>2030</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9340,7 +9306,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="43">
-        <v>301283.59375</v>
+        <v>280031.91796875</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9372,7 +9338,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="45">
-        <v>0.62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9380,7 +9346,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="45">
-        <v>0.72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9414,7 +9380,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="45">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9422,7 +9388,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="45">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9430,7 +9396,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9439,7 +9405,7 @@
       </c>
       <c r="C20" s="46">
         <f>1-frac_rice-frac_wheat-frac_maize</f>
-        <v>0.20000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9498,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="45">
-        <v>0.35675533525383901</v>
+        <v>0.57290349526853401</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9506,7 +9472,7 @@
         <v>63</v>
       </c>
       <c r="C30" s="99">
-        <v>6.5910586704521698E-2</v>
+        <v>2.97816918362898E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9514,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="99">
-        <v>9.262041217609189E-2</v>
+        <v>2.5306962187057899E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9522,7 +9488,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="99">
-        <v>0.48471366586554798</v>
+        <v>0.37200785070811798</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.25">
@@ -9531,7 +9497,7 @@
       </c>
       <c r="C33" s="48">
         <f>SUM(C29:C32)</f>
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999956</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9551,7 +9517,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="43">
-        <v>3.3282969003637</v>
+        <v>3.0092500000000002</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9559,7 +9525,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="43">
-        <v>5.6288043386920901</v>
+        <v>5.2746700000000004</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -9569,7 +9535,7 @@
         <v>61</v>
       </c>
       <c r="C39" s="43">
-        <v>6.7317453641927703</v>
+        <v>6.3242799999999999</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -9579,7 +9545,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="100">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9595,7 +9561,7 @@
         <v>57</v>
       </c>
       <c r="C42" s="43">
-        <v>5.019907774</v>
+        <v>5.4214900000000004</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,7 +9578,7 @@
         <v>52</v>
       </c>
       <c r="C45" s="45">
-        <v>6.6949000000000002E-3</v>
+        <v>6.7883000000000006E-3</v>
       </c>
       <c r="D45" s="12"/>
     </row>
@@ -9621,7 +9587,7 @@
         <v>51</v>
       </c>
       <c r="C46" s="45">
-        <v>7.2816099999999995E-2</v>
+        <v>7.293949999999999E-2</v>
       </c>
       <c r="D46" s="12"/>
     </row>
@@ -9630,7 +9596,7 @@
         <v>59</v>
       </c>
       <c r="C47" s="45">
-        <v>3.2671800000000001E-2</v>
+        <v>7.4545500000000001E-2</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
@@ -9640,7 +9606,7 @@
         <v>58</v>
       </c>
       <c r="C48" s="46">
-        <v>0.88781720000000008</v>
+        <v>0.84572670000000005</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -9744,7 +9710,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Q0vkPza2lQRkuMDA4GiuoPFnPRbgYt4FubeTFuPtoCFoJIXhf9J7v8HOttJtFAuabXSyLUBTXIeTyJ6pA2wo6Q==" saltValue="bFn1U+lDlPQU2JYvNBTCqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tzYVmbyUAIS5KMjlS59z0ZGfEr5OwokgXV9a9tkT148l2z6opN/g8bkPUrGUIK3uSoQLal6rdDQ23I1712rzrw==" saltValue="3if+d4MZZeQwRmR2TjMi8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -9776,7 +9742,7 @@
       </c>
       <c r="B1" s="22" t="str">
         <f>"Cobertura de referencia ("&amp;start_year&amp;")"</f>
-        <v>Cobertura de referencia (2021)</v>
+        <v>Cobertura de referencia (2024)</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>194</v>
@@ -9874,7 +9840,7 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="56">
-        <v>7.6012727459732039</v>
+        <v>8.0641902562029717</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>183</v>
@@ -10167,7 +10133,7 @@
         <v>151</v>
       </c>
       <c r="B18" s="98">
-        <v>0</v>
+        <v>0.1167362757</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10190,7 +10156,7 @@
         <v>152</v>
       </c>
       <c r="B19" s="98">
-        <v>0</v>
+        <v>0.86055859999999995</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10236,7 +10202,7 @@
         <v>182</v>
       </c>
       <c r="B21" s="45">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10305,7 +10271,7 @@
         <v>188</v>
       </c>
       <c r="B24" s="45">
-        <v>0</v>
+        <v>0.88458900839999999</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10397,7 +10363,7 @@
         <v>192</v>
       </c>
       <c r="B28" s="45">
-        <v>0</v>
+        <v>0.69369273269999998</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10535,7 +10501,7 @@
         <v>198</v>
       </c>
       <c r="B34" s="45">
-        <v>0.86003698112403693</v>
+        <v>0</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10669,7 +10635,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hlphXUfCvfLss6sJJELKC5Eavz2Z+xdCRR1f6CpCXuhOhkOX4DjZZIc42ddCSUCSA5ZFBN18S/uKC32He1hdDg==" saltValue="6RcF/DzxFM+giHgstthX0Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hvKw2PsgdBBWWp+IhG/RZWmDXdF5RDsOJEW6e0UsqYABsMIu8Zhid3dwU1vydDrmbjRqtTDzCxqfgCl8vtuaUg==" saltValue="rlUPwuIlSzmjP9SqiRUqHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10702,7 +10668,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>178</v>
       </c>
@@ -10711,7 +10677,7 @@
       </c>
       <c r="C2" s="47"/>
     </row>
-    <row r="3" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
         <v>179</v>
       </c>
@@ -10720,7 +10686,7 @@
       </c>
       <c r="C3" s="47"/>
     </row>
-    <row r="4" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>193</v>
       </c>
@@ -10729,7 +10695,7 @@
       </c>
       <c r="C4" s="47"/>
     </row>
-    <row r="5" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
         <v>190</v>
       </c>
@@ -10738,83 +10704,99 @@
       </c>
       <c r="C5" s="47"/>
     </row>
-    <row r="6" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C6" s="58"/>
     </row>
-    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C7" s="58"/>
     </row>
-    <row r="8" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C8" s="58"/>
     </row>
-    <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C9" s="58"/>
     </row>
-    <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
     </row>
-    <row r="11" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
     </row>
-    <row r="13" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="59"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="59"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
     </row>
-    <row r="15" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="59"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
     </row>
-    <row r="16" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="59"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
     </row>
-    <row r="17" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
     </row>
-    <row r="18" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
     </row>
-    <row r="19" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
     </row>
-    <row r="20" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JycmFFVn5zVX72Ho/nZO1W5a93GuTi4TBbBtfu2uNhKM4X4Vkh1fwZrKXs99zJYjrtj4E51DKByETnlmuCthxw==" saltValue="6FkpRYqnNdONhBo+ILlNkw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="V/E/nU0TgyXIE25PyrkzP5mkz//2nS432/1q5wf15ZMoeQvpY4664pLOkNzh5ggYnMXOQ0KXuRdH+BAZxWkezg==" saltValue="OvHssTmoD39b5swaYahpPw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -10839,78 +10821,78 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
     </row>
-    <row r="11" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
     </row>
-    <row r="12" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
     </row>
-    <row r="13" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
     </row>
-    <row r="14" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
     </row>
-    <row r="15" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
     </row>
-    <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
-    <row r="17" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
     </row>
-    <row r="18" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
     </row>
-    <row r="19" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1/UVdp0hjIZgFXDOu01KWN+OJs/aQ5en/686oScBbrZrwF6Btewl6fDWQdOtRygJU5Qv6cWgnS59L+oEM2x8jw==" saltValue="z51CQxXXUARNYYQTnbdzMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="51x66Vm4ZH8K5Hg/EGx0OsUfknh0VwwJL4oBaVS5I4HxNHw42kbe0zqC9apDKiZmfaE3JarnbCieR5zLRwruZw==" saltValue="776b6BFzvj1TEHN7DePuKA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -10975,23 +10957,23 @@
       </c>
       <c r="B3" s="21">
         <f>frac_mam_1month * 2.6</f>
-        <v>0.18201947558038559</v>
+        <v>0.181607496744186</v>
       </c>
       <c r="C3" s="21">
         <f>frac_mam_1_5months * 2.6</f>
-        <v>0.18201947558038559</v>
+        <v>0.181607496744186</v>
       </c>
       <c r="D3" s="21">
         <f>frac_mam_6_11months * 2.6</f>
-        <v>0.10527129588199952</v>
+        <v>0.10511125813953492</v>
       </c>
       <c r="E3" s="21">
         <f>frac_mam_12_23months * 2.6</f>
-        <v>5.6188773086799863E-2</v>
+        <v>5.5461126046511641E-2</v>
       </c>
       <c r="F3" s="21">
         <f>frac_mam_24_59months * 2.6</f>
-        <v>4.7173474617443208E-2</v>
+        <v>4.6551482325581484E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11000,27 +10982,27 @@
       </c>
       <c r="B4" s="21">
         <f>frac_sam_1month * 2.6</f>
-        <v>0.11838290131538888</v>
+        <v>0.12019062325581402</v>
       </c>
       <c r="C4" s="21">
         <f>frac_sam_1_5months * 2.6</f>
-        <v>0.11838290131538888</v>
+        <v>0.12019062325581402</v>
       </c>
       <c r="D4" s="21">
         <f>frac_sam_6_11months * 2.6</f>
-        <v>5.3628706098394707E-2</v>
+        <v>5.3311276744185981E-2</v>
       </c>
       <c r="E4" s="21">
         <f>frac_sam_12_23months * 2.6</f>
-        <v>3.5214787126157339E-2</v>
+        <v>3.5488065116279104E-2</v>
       </c>
       <c r="F4" s="21">
         <f>frac_sam_24_59months * 2.6</f>
-        <v>3.1943934111073664E-2</v>
+        <v>3.2146019069767461E-2</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5Lak0fw2KpKKvYCS4GTkCrUZZEsj7kwrW7eDppbTWjMVM7jiOjHSAM6AsIugafQYsQ9t1LVFqZmC2TN8WjUBWA==" saltValue="XZndPUgBD8pBVwwsF4ut4w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="28hhnaW4LMEnNxTQac0qTGcAP/8bW2D2C5d8xe1PiUoi0Kwys2eMoEcWtUOh9byPRBLaoF6wl8kpT8T9lWjTfg==" saltValue="iCLs7vRQXS8vMv0uB5uyRA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -11473,19 +11455,19 @@
       </c>
       <c r="D10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="E10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="F10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="G10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="H10" s="61">
         <v>0</v>
@@ -11819,19 +11801,19 @@
       </c>
       <c r="H18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="I18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="J18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="K18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="L18" s="61">
         <v>0</v>
@@ -12298,47 +12280,47 @@
       </c>
       <c r="E30" s="60">
         <f t="shared" ref="E30:O30" si="0">frac_maize</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12353,47 +12335,47 @@
       </c>
       <c r="E31" s="60">
         <f t="shared" ref="E31:O31" si="1">frac_rice</f>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="J31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="K31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="O31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12408,47 +12390,47 @@
       </c>
       <c r="E32" s="60">
         <f t="shared" ref="E32:O32" si="2">frac_wheat</f>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="I32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="K32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="L32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="M32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="N32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="O32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12776,7 +12758,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ieNzq2o0Mr2JKAZW6jPhp8AvRVDQZs9EeeuWHkseXJ6/BZaTZ4HXJpFmh8LZOYjOEd/sTvMIYsNkbmAFISxyxw==" saltValue="FJW5zt8Kotasgv+rCyHmZg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jhUrDRQExxsAluwXEfBK04LJFglL1+HdFxXOtD/oWe9VU8FZKkg6ouY5/SoW5ybsUOE5Kg14eQok11VbWaRkmg==" saltValue="IVPgCQhvDhT5Z9aKbqlZgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12808,7 +12790,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eAkjA1kYNtfnv/fXDvz1+lNcwD7MpHHBRoPpxZ1wKIcRtsYxMKHh43PBtamk71beohxjIXSkCsCdLZdUjysWJQ==" saltValue="tQK+MhP5O0ipzRBJhgBk6g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6wKe5Py6t/930vP08eIuQFk9i4oT1YziNGY7ADubovyQMQvvbSJUE1AFMXfVS4SX7O6RE80dJcxbug5Gxa+7ow==" saltValue="E+T3YEWj4YLCqHCeZJ5k7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13009,7 +12991,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+3Ugg+GCqp8v41se+FmNItJ68Gfd1QTPqn48NFj0twyVkin2482ACeoSyU1lYpSAyquMXUBeEZX+ALrsrAcULg==" saltValue="6Ra7k3YiImbIPRyWwPjRHA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xOCkVtVTWz4E288u1dqyLEuR2d8UdS9WYEbIYgB9dlmtloSEAEOoPxsDYWlt5l2xiwdXHPmNHzM4KJEsaC2Jyg==" saltValue="cScPxA6RB3VkRan1eYM4hQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14819,7 +14801,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ON1v4esj5QpKWFutYhT3pZq8rSTrXsfN+mWkJvtzkTamUOqt4E39Ora+q/w1GHGMUaRShZCF7Xn+F8VejaUUJg==" saltValue="m/6/QSL7rocB9eHugAonEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1gzKnYQiXpq7SHlcZk8OhnX3uaXDkJHWpzlXYRsBHo4WJOpA+3GGRdTHA6aFowA+OFxy4OuwkSuWso958t+ebg==" saltValue="Bsdgn5Et9LHqwKK8H4VGsA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14881,7 +14863,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>165</v>
       </c>
@@ -14898,7 +14880,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>166</v>
       </c>
@@ -14915,7 +14897,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>167</v>
       </c>
@@ -14932,7 +14914,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>169</v>
       </c>
@@ -14949,7 +14931,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>170</v>
       </c>
@@ -14968,7 +14950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>171</v>
       </c>
@@ -14987,7 +14969,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>172</v>
       </c>
@@ -15006,7 +14988,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>173</v>
       </c>
@@ -15025,7 +15007,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>174</v>
       </c>
@@ -15042,7 +15024,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>175</v>
       </c>
@@ -15059,7 +15041,7 @@
       <c r="J11" s="87"/>
       <c r="K11" s="87"/>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>176</v>
       </c>
@@ -15076,7 +15058,7 @@
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>177</v>
       </c>
@@ -15093,7 +15075,7 @@
       <c r="J13" s="87"/>
       <c r="K13" s="87"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>178</v>
       </c>
@@ -15112,7 +15094,7 @@
       <c r="J14" s="87"/>
       <c r="K14" s="87"/>
     </row>
-    <row r="15" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>179</v>
       </c>
@@ -15131,7 +15113,7 @@
       <c r="J15" s="87"/>
       <c r="K15" s="87"/>
     </row>
-    <row r="16" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>180</v>
       </c>
@@ -15152,7 +15134,7 @@
       <c r="J16" s="87"/>
       <c r="K16" s="87"/>
     </row>
-    <row r="17" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>181</v>
       </c>
@@ -15169,7 +15151,7 @@
       <c r="J17" s="87"/>
       <c r="K17" s="87"/>
     </row>
-    <row r="18" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>151</v>
       </c>
@@ -15188,7 +15170,7 @@
       <c r="J18" s="87"/>
       <c r="K18" s="87"/>
     </row>
-    <row r="19" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>152</v>
       </c>
@@ -15207,7 +15189,7 @@
       <c r="J19" s="87"/>
       <c r="K19" s="87"/>
     </row>
-    <row r="20" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>153</v>
       </c>
@@ -15226,7 +15208,7 @@
       <c r="J20" s="87"/>
       <c r="K20" s="87"/>
     </row>
-    <row r="21" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>182</v>
       </c>
@@ -15245,7 +15227,7 @@
       <c r="J21" s="87"/>
       <c r="K21" s="87"/>
     </row>
-    <row r="22" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>184</v>
       </c>
@@ -15582,7 +15564,7 @@
       <c r="K39" s="87"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KUZq5VUXw6O1CkP12vv+F3Ib2xy7MxPd8SCvMp7tyv80senNUfOuVGCYv6O24AqWh+jCZ0JrWKHvsh8YD+MyEg==" saltValue="mTduvPixnbQEIH9P0kUObA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0Pd+oq0OSlixHo64PKe2gJXspbz8vzt8u+lilDbjTezWjJIazhmsrr8tWOiU0IUgqp4ahManv9myDBvna1aEyw==" saltValue="wx6k7PYx640A8BF6euLubA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15644,7 +15626,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>78</v>
       </c>
@@ -15673,7 +15655,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>74</v>
       </c>
@@ -15702,7 +15684,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>77</v>
       </c>
@@ -15731,7 +15713,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>75</v>
       </c>
@@ -15760,7 +15742,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>76</v>
       </c>
@@ -15789,7 +15771,7 @@
       <c r="J6" s="87"/>
       <c r="K6" s="87"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>113</v>
       </c>
@@ -15810,7 +15792,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>114</v>
       </c>
@@ -15831,7 +15813,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>115</v>
       </c>
@@ -15852,7 +15834,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>116</v>
       </c>
@@ -15873,7 +15855,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>68</v>
       </c>
@@ -15894,7 +15876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>69</v>
       </c>
@@ -15913,7 +15895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>70</v>
       </c>
@@ -15932,7 +15914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>71</v>
       </c>
@@ -15952,7 +15934,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NwFAsltnEMb1iSwCjMqukMtjHd4LSN8BpRu8Y8iyHojp1F/dglN8LspXMk7wH8/lER+JSZtPRTf7TDRjTvVpDg==" saltValue="5lhUvP/T5Qjq7s88qVP31A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/do7wEkf4+fOjN6c/nPOnlUPWCpsw7AtS2dGz5F7OfPbTi4Bwxbz/9qCgPT8FTghGlcnnGArfG/ehNP4i9rAnA==" saltValue="2yrojO1MICvcUixvbNWk4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16003,360 +15985,398 @@
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>start_year</f>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>62199.62</v>
+        <v>54467</v>
       </c>
       <c r="C2" s="49">
-        <v>154000</v>
+        <v>192433.5</v>
       </c>
       <c r="D2" s="49">
-        <v>317000</v>
+        <v>293127.5</v>
       </c>
       <c r="E2" s="49">
-        <v>452000</v>
+        <v>420551</v>
       </c>
       <c r="F2" s="49">
-        <v>510000</v>
+        <v>443005.5</v>
       </c>
       <c r="G2" s="17">
-        <f t="shared" ref="G2:G11" si="0">C2+D2+E2+F2</f>
-        <v>1433000</v>
+        <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
+        <v>1349117.5</v>
       </c>
       <c r="H2" s="17">
-        <f t="shared" ref="H2:H11" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>71037.990524519744</v>
+        <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
+        <v>62231.70675768792</v>
       </c>
       <c r="I2" s="17">
-        <f t="shared" ref="I2:I11" si="2">G2-H2</f>
-        <v>1361962.0094754803</v>
+        <f t="shared" ref="I2:I13" si="2">G2-H2</f>
+        <v>1286885.793242312</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A40" si="3">IF($A$2+ROW(A3)-2&lt;=end_year,A2+1,"")</f>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>61197.364999999998</v>
+        <v>53514</v>
       </c>
       <c r="C3" s="50">
-        <v>159000</v>
+        <v>192820.5</v>
       </c>
       <c r="D3" s="50">
-        <v>305000</v>
+        <v>291767.5</v>
       </c>
       <c r="E3" s="50">
-        <v>445000</v>
+        <v>404953</v>
       </c>
       <c r="F3" s="50">
-        <v>503000</v>
+        <v>433742</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>1412000</v>
+        <v>1323283</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>69893.318238850581</v>
+        <v>61142.848980683928</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>1342106.6817611493</v>
+        <v>1262140.1510193162</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="3"/>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>60203.25</v>
+        <v>52777</v>
       </c>
       <c r="C4" s="50">
-        <v>163000</v>
+        <v>191931</v>
       </c>
       <c r="D4" s="50">
-        <v>296000</v>
+        <v>292391.5</v>
       </c>
       <c r="E4" s="50">
-        <v>437000</v>
+        <v>387164</v>
       </c>
       <c r="F4" s="50">
-        <v>495000</v>
+        <v>425960.5</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>1391000</v>
+        <v>1297447</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>68757.942621599504</v>
+        <v>60300.783732360789</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>1322242.0573784006</v>
+        <v>1237146.2162676393</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="3"/>
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>59208.430000000008</v>
+        <v>51930</v>
       </c>
       <c r="C5" s="50">
-        <v>167000</v>
+        <v>190255</v>
       </c>
       <c r="D5" s="50">
-        <v>289000</v>
+        <v>295527.5</v>
       </c>
       <c r="E5" s="50">
-        <v>427000</v>
+        <v>367359</v>
       </c>
       <c r="F5" s="50">
-        <v>485000</v>
+        <v>419269.5</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>1368000</v>
+        <v>1272411</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>67621.761826064059</v>
+        <v>59333.037103690927</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>1300378.238173936</v>
+        <v>1213077.9628963091</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="3"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>58213.127000000008</v>
+        <v>51269</v>
       </c>
       <c r="C6" s="50">
-        <v>168000</v>
+        <v>187972</v>
       </c>
       <c r="D6" s="50">
-        <v>286000</v>
+        <v>300750.5</v>
       </c>
       <c r="E6" s="50">
-        <v>413000</v>
+        <v>346546.5</v>
       </c>
       <c r="F6" s="50">
-        <v>478000</v>
+        <v>413740</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>1345000</v>
+        <v>1249009</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>66485.029397746548</v>
+        <v>58577.806263607352</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>1278514.9706022535</v>
+        <v>1190431.1937363925</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="3"/>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>57255.721199999993</v>
+        <v>50562</v>
       </c>
       <c r="C7" s="50">
-        <v>168000</v>
+        <v>184222.5</v>
       </c>
       <c r="D7" s="50">
-        <v>287000</v>
+        <v>304271.5</v>
       </c>
       <c r="E7" s="50">
-        <v>396000</v>
+        <v>329163</v>
       </c>
       <c r="F7" s="50">
-        <v>471000</v>
+        <v>408555</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>1322000</v>
+        <v>1226212</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>65391.579242447842</v>
+        <v>57770.017755378787</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>1256608.4207575521</v>
+        <v>1168441.9822446213</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="3"/>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>56297.59199999999</v>
+        <v>50043</v>
       </c>
       <c r="C8" s="50">
-        <v>166000</v>
+        <v>180464</v>
       </c>
       <c r="D8" s="50">
-        <v>291000</v>
+        <v>305340</v>
       </c>
       <c r="E8" s="50">
-        <v>377000</v>
+        <v>315686</v>
       </c>
       <c r="F8" s="50">
-        <v>464000</v>
+        <v>404969</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>1298000</v>
+        <v>1206459</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>64297.302894282599</v>
+        <v>57177.030151742831</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>1233702.6971057174</v>
+        <v>1149281.9698482573</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="3"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>55338.943999999989</v>
+        <v>49664</v>
       </c>
       <c r="C9" s="50">
-        <v>163000</v>
+        <v>178466.5</v>
       </c>
       <c r="D9" s="50">
-        <v>296000</v>
+        <v>305962.5</v>
       </c>
       <c r="E9" s="50">
-        <v>356000</v>
+        <v>303846</v>
       </c>
       <c r="F9" s="50">
-        <v>459000</v>
+        <v>402126</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>1274000</v>
+        <v>1190401</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>63202.434026267802</v>
+        <v>56744.000668548164</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>1210797.5659737322</v>
+        <v>1133656.999331452</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="3"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>54371.483599999978</v>
+        <v>49258</v>
       </c>
       <c r="C10" s="50">
-        <v>160000</v>
+        <v>177009.5</v>
       </c>
       <c r="D10" s="50">
-        <v>301000</v>
+        <v>306851</v>
       </c>
       <c r="E10" s="50">
-        <v>336000</v>
+        <v>294051</v>
       </c>
       <c r="F10" s="50">
-        <v>452000</v>
+        <v>396873</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>1249000</v>
+        <v>1174784.5</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>62097.500543908129</v>
+        <v>56280.122119268395</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>1186902.4994560918</v>
+        <v>1118504.3778807316</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="3"/>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>53412.480000000003</v>
+        <v>48909</v>
       </c>
       <c r="C11" s="50">
-        <v>158000</v>
+        <v>175290</v>
       </c>
       <c r="D11" s="50">
-        <v>306000</v>
+        <v>306873</v>
       </c>
       <c r="E11" s="50">
-        <v>318000</v>
+        <v>286635</v>
       </c>
       <c r="F11" s="50">
-        <v>445000</v>
+        <v>388061</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>1227000</v>
+        <v>1156859</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>61002.225546250935</v>
+        <v>55881.369376168295</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>1165997.7744537489</v>
+        <v>1100977.6306238316</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+        <v>2034</v>
+      </c>
+      <c r="B12" s="49">
+        <v>48679</v>
+      </c>
+      <c r="C12" s="50">
+        <v>172621</v>
+      </c>
+      <c r="D12" s="50">
+        <v>306128</v>
+      </c>
+      <c r="E12" s="50">
+        <v>281895</v>
+      </c>
+      <c r="F12" s="50">
+        <v>377076</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="0"/>
+        <v>1137720</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>55618.581035443298</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="2"/>
+        <v>1082101.4189645567</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+        <v>2035</v>
+      </c>
+      <c r="B13" s="49">
+        <v>48452</v>
+      </c>
+      <c r="C13" s="50">
+        <v>169021.5</v>
+      </c>
+      <c r="D13" s="50">
+        <v>305029</v>
+      </c>
+      <c r="E13" s="50">
+        <v>280564</v>
+      </c>
+      <c r="F13" s="50">
+        <v>364704.99999999988</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="0"/>
+        <v>1119319.5</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>55359.220368727758</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="2"/>
+        <v>1063960.2796312722</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -16763,7 +16783,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="N2N5e/tRlRtEXzkNcPh6NQshK0v2qIGrfx2biCsembBHbibuFqHGZcj/vNimeknLqxG9oxEBGBdJHwWUuGqR1Q==" saltValue="Gl65LLVp2mbc1O+F2m9PRA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="h9mfH6NXVn/VpW0/e3jtB276pS7D2FiJNXwnpT/2+Bc6Q9k5tVJns/wIaZrXoCXMaTXReEUTqzU7LQSFQWy9+g==" saltValue="ZS7FFT19MgoOZE+3d5aCyA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -16842,7 +16862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="104"/>
       <c r="C3" s="8" t="s">
         <v>149</v>
@@ -16864,7 +16884,7 @@
       </c>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="104"/>
       <c r="C4" s="8" t="s">
         <v>155</v>
@@ -16886,7 +16906,7 @@
       </c>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="103" t="s">
         <v>78</v>
       </c>
@@ -16894,9 +16914,7 @@
         <v>150</v>
       </c>
       <c r="D5" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>2.7425041224108462</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -16911,15 +16929,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="104"/>
       <c r="C6" s="8" t="s">
         <v>149</v>
       </c>
       <c r="D6" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>2.7425041224108462</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -16934,7 +16950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="104"/>
       <c r="C7" s="8" t="s">
         <v>155</v>
@@ -16955,7 +16971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="103" t="s">
         <v>74</v>
       </c>
@@ -16966,9 +16982,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>1.8840797111685363</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -16980,7 +16994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="104"/>
       <c r="C9" s="8" t="s">
         <v>149</v>
@@ -16989,9 +17003,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>1.8840797111685363</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -17003,7 +17015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="104"/>
       <c r="C10" s="8" t="s">
         <v>155</v>
@@ -17024,7 +17036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="103" t="s">
         <v>77</v>
       </c>
@@ -17047,7 +17059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="104"/>
       <c r="C12" s="8" t="s">
         <v>149</v>
@@ -17068,7 +17080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="104"/>
       <c r="C13" s="8" t="s">
         <v>155</v>
@@ -17089,7 +17101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="103" t="s">
         <v>75</v>
       </c>
@@ -17112,7 +17124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="104"/>
       <c r="C15" s="8" t="s">
         <v>149</v>
@@ -17133,7 +17145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="104"/>
       <c r="C16" s="8" t="s">
         <v>155</v>
@@ -17177,7 +17189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D18" s="86"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
@@ -17210,7 +17222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20" s="104"/>
       <c r="C20" s="8" t="s">
         <v>149</v>
@@ -17231,7 +17243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="104"/>
       <c r="C21" s="8" t="s">
         <v>155</v>
@@ -17252,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>78</v>
       </c>
@@ -17275,7 +17287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" s="104"/>
       <c r="C23" s="8" t="s">
         <v>149</v>
@@ -17296,7 +17308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" s="104"/>
       <c r="C24" s="8" t="s">
         <v>155</v>
@@ -17317,7 +17329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>74</v>
       </c>
@@ -17340,7 +17352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" s="104"/>
       <c r="C26" s="8" t="s">
         <v>149</v>
@@ -18022,9 +18034,7 @@
         <v>150</v>
       </c>
       <c r="D58" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>1.9157748853133143</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18049,9 +18059,7 @@
         <v>149</v>
       </c>
       <c r="D59" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>1.9157748853133143</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18108,9 +18116,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.5456633572312237</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18135,9 +18141,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.5456633572312237</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -19367,9 +19371,7 @@
         <v>150</v>
       </c>
       <c r="D111" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>4.347485266129171</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="88">
         <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
@@ -19394,9 +19396,7 @@
         <v>149</v>
       </c>
       <c r="D112" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>4.347485266129171</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19453,9 +19453,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>2.3183110093834931</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="88">
         <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
@@ -19480,9 +19478,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>2.3183110093834931</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="88">
         <f t="shared" si="13"/>
@@ -20584,7 +20580,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0C5biAPmFoHcTQOdUl02FkJkdwv48b2bc2YZ/rgGXrutZbXZ+Xe0Lz0JdbakZXeFMmXBwZHEXoDuYZEdoFIR2g==" saltValue="K48LDuUiVKZra+NUKtux7A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7dAfRSW9lHcnBlmY9tUGCcjsuIL9SKuFzXmMmQhjnwWCYjMZqgNQzt+5hM6EFwROwB6tVNRZ4/YeAHiB+/j7WA==" saltValue="8Fx40J+GjghVyfwIJUbJig==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -21846,7 +21842,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9Vb8+t+kb/27uUVtu2r1LC54YXmqSPwyW/nGC8QQNrrWVRxyXtOt9GdIpdkfHod6yGya+SwJ7I/D38zIX/3a2A==" saltValue="UeISDL+ZXAJS1oDZXsUEbw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sEU3vyuYdB7epZqHLLLcCdVQwZiQwkKfLJEBH9vwGZALTZ5phsHM/6mKNpfKmJ7kWvnefyciLkI7tqHsIOuTHw==" saltValue="gSQF3OQ/w6aO38YZxUpOPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -29981,7 +29977,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eKgF9hZT+3WGUk6rOsJraEcCIbuVPPOd9bS2EJyVs844we/KjTL1PYFvbYw4YeRxHJwjoc+eTW0WjNSHGAmIbg==" saltValue="Vt3jbpGzIbfcL81JGPeIBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HrxXn8jM5lfXN4n5a585LFF/ELcslB4HQ9/cJDOgktlRse04WtgW/+55Q6Tyd3Ey3zlkQl5xTJWOYjrTBOQF5Q==" saltValue="LpbMfe4UYN5jyJpRO3yWRw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30090,13 +30086,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.64, (0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)))
-/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.61180546602946062</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.64, (0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.59947505582979299</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30113,12 +30106,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.86668649691453392</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.8606074397322292</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="90">
         <v>1</v>
@@ -30135,12 +30126,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.86668649691453392</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.8606074397322292</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="90">
         <v>1</v>
@@ -30418,12 +30407,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.44, (0.44*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.44*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.41056784720494943</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.44, (0.44*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.44*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.39813359589519065</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30443,12 +30432,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.83398602669595534</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.82671397570780047</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="90">
         <f>IF(G7=1,1,G7*0.9)</f>
@@ -30468,12 +30455,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.83398602669595534</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.82671397570780047</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="90">
         <f>IF(G8=1,1,G8*0.9)</f>
@@ -30530,12 +30515,10 @@
         <v>303</v>
       </c>
       <c r="C35" s="90">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="90">
-        <f>D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="90">
         <v>1</v>
@@ -30795,12 +30778,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.92, (0.92*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.92*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.91067386012528218</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.92, (0.92*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.92*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.90638395421164486</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -30820,12 +30803,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.89963526866308052</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.89487642775076093</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="90">
         <f>IF(G7=1,1,G7*1.1)</f>
@@ -30845,12 +30826,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.89963526866308052</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.89487642775076093</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="90">
         <f>IF(G8=1,1,G8*1.1)</f>
@@ -30907,12 +30886,10 @@
         <v>304</v>
       </c>
       <c r="C58" s="90">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="90">
-        <f>D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="90">
         <v>1</v>
@@ -31068,7 +31045,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QQBHpwFreYXxzw5l7Uzc/cUXb4BuGo/KdgF6mHXyy2CiMhPrlMz10eK3UVV7MhxcNs/uwND9mrcxPNCxZM/Hmg==" saltValue="mfdU9UoDcmvUY4cZbHLzmg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rhlXwYcoxiC8rw0hK+rGqFq/utkU0Z1fFgpwMr2VX1AURoe7EiVFOy/7s/Vl+ZSPpS+eqx4iLBGosajugKalqg==" saltValue="NMDcl3SXOgGkT4f7O2kHmw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31889,7 +31866,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pmdmgFpYU4tCbBiDg9vyskTpXQehTuymu4R7WaMkRDzFVBrZWKJaa+FgkjZf9Li4HJoiiALqOtB6v89n5xAnCQ==" saltValue="8SmZ3WNFBZZ3IZ++7az/bw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2d4ag+oglePZTk6QNaCjEnvVFmna/+CA8wD25Ni/Ht7FoMLYW9y1hDlf/gKun54/D2Rg2yzMo7p2NWd/JhhSpA==" saltValue="QyknO+UGx72lJ0CqTrRQSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31964,7 +31941,7 @@
         <v>169</v>
       </c>
       <c r="C3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="90">
         <v>0.53</v>
@@ -32299,16 +32276,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -32475,15 +32452,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="90">
+        <f>M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="90">
+        <f>N8</f>
         <v>0.51</v>
       </c>
       <c r="O14" s="90">
+        <f>O8</f>
         <v>0.51</v>
       </c>
     </row>
@@ -32592,59 +32573,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.72,(0.72*'Distribución estado nutricional'!E$14/(1-0.72*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.61929050097959004</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.72,(0.72*'Distribución estado nutricional'!F$14/(1-0.72*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.68105597818936314</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.72,(0.72*'Distribución estado nutricional'!G$14/(1-0.72*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.68105597818936314</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.72,(0.72*'Distribución estado nutricional'!H$14/(1-0.72*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.64929859719438865</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.72,(0.72*'Distribución estado nutricional'!I$14/(1-0.72*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.64929859719438865</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.72,(0.72*'Distribución estado nutricional'!J$14/(1-0.72*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.64929859719438865</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.72,(0.72*'Distribución estado nutricional'!K$14/(1-0.72*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.64929859719438865</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.72,(0.72*'Distribución estado nutricional'!L$14/(1-0.72*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.65428684314500196</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.72,(0.72*'Distribución estado nutricional'!M$14/(1-0.72*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.65428684314500196</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.72,(0.72*'Distribución estado nutricional'!N$14/(1-0.72*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.65428684314500196</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.72,(0.72*'Distribución estado nutricional'!O$14/(1-0.72*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.65428684314500196</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -32658,37 +32617,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <v>1</v>
+        <f t="shared" ref="E20:O20" si="0">E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -32702,59 +32672,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.8,(0.8*'Distribución estado nutricional'!E$14/(1-0.8*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.71674460013823738</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.8,(0.8*'Distribución estado nutricional'!F$14/(1-0.8*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.76860689790719061</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.8,(0.8*'Distribución estado nutricional'!G$14/(1-0.8*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.76860689790719061</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.8,(0.8*'Distribución estado nutricional'!H$14/(1-0.8*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.74226804123711332</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.8,(0.8*'Distribución estado nutricional'!I$14/(1-0.8*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.74226804123711332</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.8,(0.8*'Distribución estado nutricional'!J$14/(1-0.8*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.74226804123711332</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.8,(0.8*'Distribución estado nutricional'!K$14/(1-0.8*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.74226804123711332</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.8,(0.8*'Distribución estado nutricional'!L$14/(1-0.8*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.74645030425963499</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.8,(0.8*'Distribución estado nutricional'!M$14/(1-0.8*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.74645030425963499</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.8,(0.8*'Distribución estado nutricional'!N$14/(1-0.8*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.74645030425963499</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.8,(0.8*'Distribución estado nutricional'!O$14/(1-0.8*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.74645030425963499</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -32815,53 +32763,53 @@
         <v>169</v>
       </c>
       <c r="C26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="90">
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -32870,23 +32818,23 @@
         <v>174</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32902,19 +32850,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32923,23 +32871,23 @@
         <v>175</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32955,19 +32903,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32976,23 +32924,23 @@
         <v>176</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -33008,19 +32956,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33029,23 +32977,23 @@
         <v>177</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33061,19 +33009,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33082,39 +33030,39 @@
         <v>178</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33135,39 +33083,39 @@
         <v>179</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33188,39 +33136,39 @@
         <v>180</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33258,19 +33206,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33339,11 +33287,11 @@
         <v>190</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33356,35 +33304,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -33393,56 +33341,52 @@
         <v>191</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="90">
-        <f>M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="90">
-        <f>N32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="90">
-        <f>O32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -33450,11 +33394,11 @@
         <v>204</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33464,39 +33408,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33511,55 +33455,55 @@
         <v>171</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33568,67 +33512,45 @@
         <v>172</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.54,(0.54*'Distribución estado nutricional'!E$14/(1-0.54*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.42614890867999877</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.54,(0.54*'Distribución estado nutricional'!F$14/(1-0.54*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.49362782922447318</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.54,(0.54*'Distribución estado nutricional'!G$14/(1-0.54*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.49362782922447318</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.54,(0.54*'Distribución estado nutricional'!H$14/(1-0.54*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.4580584354382658</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.54,(0.54*'Distribución estado nutricional'!I$14/(1-0.54*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.4580584354382658</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.54,(0.54*'Distribución estado nutricional'!J$14/(1-0.54*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.4580584354382658</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.54,(0.54*'Distribución estado nutricional'!K$14/(1-0.54*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.4580584354382658</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.54,(0.54*'Distribución estado nutricional'!L$14/(1-0.54*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.46351931330472107</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.54,(0.54*'Distribución estado nutricional'!M$14/(1-0.54*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.46351931330472107</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.54,(0.54*'Distribución estado nutricional'!N$14/(1-0.54*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.46351931330472107</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.54,(0.54*'Distribución estado nutricional'!O$14/(1-0.54*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.46351931330472107</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -33636,56 +33558,56 @@
         <v>173</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33693,67 +33615,45 @@
         <v>181</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.7,(0.7*'Distribución estado nutricional'!E$14/(1-0.7*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.59613201910770042</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.7,(0.7*'Distribución estado nutricional'!F$14/(1-0.7*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.65958943659236502</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.7,(0.7*'Distribución estado nutricional'!G$14/(1-0.7*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.65958943659236502</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.7,(0.7*'Distribución estado nutricional'!H$14/(1-0.7*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.62686567164179097</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.7,(0.7*'Distribución estado nutricional'!I$14/(1-0.7*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.62686567164179097</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.7,(0.7*'Distribución estado nutricional'!J$14/(1-0.7*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.62686567164179097</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.7,(0.7*'Distribución estado nutricional'!K$14/(1-0.7*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.62686567164179097</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.7,(0.7*'Distribución estado nutricional'!L$14/(1-0.7*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.63199214916584878</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.7,(0.7*'Distribución estado nutricional'!M$14/(1-0.7*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.63199214916584878</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.7,(0.7*'Distribución estado nutricional'!N$14/(1-0.7*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.63199214916584878</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.7,(0.7*'Distribución estado nutricional'!O$14/(1-0.7*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.63199214916584878</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -33814,53 +33714,53 @@
         <v>169</v>
       </c>
       <c r="C49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="90">
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -33869,23 +33769,23 @@
         <v>174</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33901,19 +33801,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33922,23 +33822,23 @@
         <v>175</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33954,19 +33854,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33975,23 +33875,23 @@
         <v>176</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -34007,19 +33907,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34028,23 +33928,23 @@
         <v>177</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -34060,19 +33960,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34081,39 +33981,39 @@
         <v>178</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34134,39 +34034,39 @@
         <v>179</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34187,52 +34087,52 @@
         <v>180</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -34258,19 +34158,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34339,11 +34239,11 @@
         <v>190</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34356,35 +34256,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34393,56 +34293,52 @@
         <v>191</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="90">
-        <f>M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="90">
-        <f>N54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="90">
-        <f>O54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34450,11 +34346,11 @@
         <v>204</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34464,39 +34360,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34511,55 +34407,55 @@
         <v>171</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -34568,67 +34464,45 @@
         <v>172</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.97,(0.97*'Distribución estado nutricional'!E$14/(1-0.97*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.95338848876426263</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.97,(0.97*'Distribución estado nutricional'!F$14/(1-0.97*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.96409336265846413</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.97,(0.97*'Distribución estado nutricional'!G$14/(1-0.97*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.96409336265846413</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.97,(0.97*'Distribución estado nutricional'!H$14/(1-0.97*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.95881383855024704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.97,(0.97*'Distribución estado nutricional'!I$14/(1-0.97*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.95881383855024704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.97,(0.97*'Distribución estado nutricional'!J$14/(1-0.97*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.95881383855024704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.97,(0.97*'Distribución estado nutricional'!K$14/(1-0.97*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.95881383855024704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.97,(0.97*'Distribución estado nutricional'!L$14/(1-0.97*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.95967308312721811</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.97,(0.97*'Distribución estado nutricional'!M$14/(1-0.97*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.95967308312721811</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.97,(0.97*'Distribución estado nutricional'!N$14/(1-0.97*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.95967308312721811</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.97,(0.97*'Distribución estado nutricional'!O$14/(1-0.97*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.95967308312721811</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -34636,56 +34510,56 @@
         <v>173</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34693,71 +34567,49 @@
         <v>181</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.92,(0.92*'Distribución estado nutricional'!E$14/(1-0.92*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.87915189721539444</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.92,(0.92*'Distribución estado nutricional'!F$14/(1-0.92*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.90521096783996757</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.92,(0.92*'Distribución estado nutricional'!G$14/(1-0.92*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.90521096783996757</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.92,(0.92*'Distribución estado nutricional'!H$14/(1-0.92*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.89224137931034486</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.92,(0.92*'Distribución estado nutricional'!I$14/(1-0.92*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.89224137931034486</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.92,(0.92*'Distribución estado nutricional'!J$14/(1-0.92*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.89224137931034486</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.92,(0.92*'Distribución estado nutricional'!K$14/(1-0.92*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.89224137931034486</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.92,(0.92*'Distribución estado nutricional'!L$14/(1-0.92*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.89433643279797115</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.92,(0.92*'Distribución estado nutricional'!M$14/(1-0.92*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.89433643279797115</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.92,(0.92*'Distribución estado nutricional'!N$14/(1-0.92*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.89433643279797115</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.92,(0.92*'Distribución estado nutricional'!O$14/(1-0.92*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.89433643279797115</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b95XscosDl5zIZa8n+G5TKGXbsmA4u6uVyavu7QJHGp4vTLai9wZIV6kWdeyr8PncRHB8YZHgqloy7fMhZteeQ==" saltValue="ZQP97XvDzTTYwRpLfGfN0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JR9iaLSV14Y+J1gOdjW2PZXRQaLRonVMqC0y6p2kux9firlN9dWlPNYVCKdNp/IPoeHB4ndRUTJQ7asHDRS08Q==" saltValue="h+wl5Re10NiYXCO69pZbpg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34803,7 +34655,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>164</v>
       </c>
@@ -34811,24 +34663,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$11/(1-(1/1.33)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.74308431935566976</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$11/(1-(1/1.33)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.74797108601609574</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$11/(1-(1/1.33)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.74932695257275428</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$11/(1-(1/1.33)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.74956626993277686</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34842,7 +34690,7 @@
       <c r="F4" s="83"/>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>162</v>
       </c>
@@ -34850,24 +34698,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$10/(1-(1/1.33)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.73809368108132856</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$10/(1-(1/1.33)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.74408904635016893</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$10/(1-(1/1.33)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.74778141914166463</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$10/(1-(1/1.33)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.74844806863821167</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34899,7 +34743,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>164</v>
       </c>
@@ -34907,24 +34751,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$11/(1-(1/1.54)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.63866743316646069</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$11/(1-(1/1.54)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.64459036998182218</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$11/(1-(1/1.54)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.64623935922615783</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$11/(1-(1/1.54)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.64653066907659762</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34938,7 +34778,7 @@
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>162</v>
       </c>
@@ -34946,24 +34786,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$10/(1-(1/1.54)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.63265118934293785</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$10/(1-(1/1.54)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.63988261134532487</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$10/(1-(1/1.54)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.64435989481245026</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$10/(1-(1/1.54)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.64517019106258211</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34995,7 +34831,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>164</v>
       </c>
@@ -35003,24 +34839,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$11/(1-(1/1.16)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.8564337571762517</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$11/(1-(1/1.16)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.85957195816190024</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$11/(1-(1/1.16)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.8604394579645257</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$11/(1-(1/1.16)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.86059243163848642</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -35034,7 +34866,7 @@
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>162</v>
       </c>
@@ -35042,28 +34874,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$10/(1-(1/1.16)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.85321000041621853</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$10/(1-(1/1.16)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.85708046256201842</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$10/(1-(1/1.16)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.85945049595820067</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$10/(1-(1/1.16)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.85987729614939534</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zlzXWPW37bdYtmGwTVBlngTVPVoYE27BduHitFFp7UZ8UvygvuoJr2sLMk+Xhdl7wMnN/SFdT4qs645jA76uYQ==" saltValue="XACyyTATRm7ATOufpO5Djw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MTA2xK2iSNnLIVuSVB11lCBlj9dLFB2INpY6td96VgJziNGIhAhjUhVsPOOU1YX6WFNZlKkXoOyEvYDimTg6Pg==" saltValue="dUjdkdBIGWM2NBuXylaDeA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -35116,7 +34944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>196</v>
       </c>
@@ -35142,7 +34970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>339</v>
       </c>
@@ -35162,7 +34990,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>338</v>
       </c>
@@ -35182,7 +35010,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>193</v>
       </c>
@@ -35208,7 +35036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>338</v>
       </c>
@@ -35228,7 +35056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
@@ -35251,7 +35079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>338</v>
       </c>
@@ -35271,7 +35099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>184</v>
       </c>
@@ -35297,7 +35125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>338</v>
       </c>
@@ -35317,7 +35145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
@@ -35340,7 +35168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>338</v>
       </c>
@@ -35360,7 +35188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>204</v>
       </c>
@@ -35386,7 +35214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>338</v>
       </c>
@@ -35406,7 +35234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -35429,7 +35257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>338</v>
       </c>
@@ -35449,7 +35277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>167</v>
       </c>
@@ -35475,7 +35303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>338</v>
       </c>
@@ -35495,7 +35323,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
@@ -35518,7 +35346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>338</v>
       </c>
@@ -35538,7 +35366,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>173</v>
       </c>
@@ -35564,7 +35392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>339</v>
       </c>
@@ -35584,7 +35412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>171</v>
       </c>
@@ -35610,7 +35438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>339</v>
       </c>
@@ -35630,7 +35458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>172</v>
       </c>
@@ -35656,7 +35484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>339</v>
       </c>
@@ -35676,7 +35504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>200</v>
       </c>
@@ -35702,7 +35530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>339</v>
       </c>
@@ -35722,7 +35550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>338</v>
       </c>
@@ -35742,7 +35570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>201</v>
       </c>
@@ -35768,7 +35596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>339</v>
       </c>
@@ -35788,7 +35616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>338</v>
       </c>
@@ -35808,7 +35636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>199</v>
       </c>
@@ -35834,7 +35662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>339</v>
       </c>
@@ -35854,7 +35682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C35" s="5" t="s">
         <v>338</v>
       </c>
@@ -35874,7 +35702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>198</v>
       </c>
@@ -35900,7 +35728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>339</v>
       </c>
@@ -35920,7 +35748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>338</v>
       </c>
@@ -35940,7 +35768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>197</v>
       </c>
@@ -35966,7 +35794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>339</v>
       </c>
@@ -35986,7 +35814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>338</v>
       </c>
@@ -36006,7 +35834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>203</v>
       </c>
@@ -36032,7 +35860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>339</v>
       </c>
@@ -36052,7 +35880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>338</v>
       </c>
@@ -36072,7 +35900,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>102</v>
       </c>
@@ -36095,7 +35923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>339</v>
       </c>
@@ -36115,7 +35943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C47" s="5" t="s">
         <v>338</v>
       </c>
@@ -36135,7 +35963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>192</v>
       </c>
@@ -36161,7 +35989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="5" t="s">
         <v>339</v>
       </c>
@@ -36181,7 +36009,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>202</v>
       </c>
@@ -36207,7 +36035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C51" s="5" t="s">
         <v>339</v>
       </c>
@@ -36227,7 +36055,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>182</v>
       </c>
@@ -36253,12 +36081,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C53" s="5" t="s">
         <v>339</v>
       </c>
       <c r="D53" s="90">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="90">
         <v>0</v>
@@ -36306,7 +36134,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>196</v>
       </c>
@@ -36337,7 +36165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
         <v>339</v>
       </c>
@@ -36359,7 +36187,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C59" s="5" t="s">
         <v>338</v>
       </c>
@@ -36381,7 +36209,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>193</v>
       </c>
@@ -36407,7 +36235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C61" s="5" t="s">
         <v>338</v>
       </c>
@@ -36427,7 +36255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>6</v>
       </c>
@@ -36450,7 +36278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" s="5" t="s">
         <v>338</v>
       </c>
@@ -36470,7 +36298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>184</v>
       </c>
@@ -36496,7 +36324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C65" s="5" t="s">
         <v>338</v>
       </c>
@@ -36516,7 +36344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>6</v>
       </c>
@@ -36539,7 +36367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C67" s="5" t="s">
         <v>338</v>
       </c>
@@ -36559,7 +36387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>204</v>
       </c>
@@ -36585,7 +36413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C69" s="5" t="s">
         <v>338</v>
       </c>
@@ -36608,7 +36436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>6</v>
       </c>
@@ -36636,7 +36464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C71" s="5" t="s">
         <v>338</v>
       </c>
@@ -36659,7 +36487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>167</v>
       </c>
@@ -36690,7 +36518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" s="5" t="s">
         <v>338</v>
       </c>
@@ -37514,7 +37342,7 @@
         <v>339</v>
       </c>
       <c r="D108" s="90">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="90">
         <v>0</v>
@@ -38775,7 +38603,7 @@
         <v>339</v>
       </c>
       <c r="D163" s="90">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="90">
         <v>0</v>
@@ -38791,7 +38619,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NKMyMd0vFeoubexP7GUwM6ZzMINf51KBAzpJv0MIsprEC4fd0YK11C19UY2LY6mU9Fz7l1Gtkqb4VPP/ImNJgg==" saltValue="W0l0NbgZO9REGMAfVhceZg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JJJv8y8tPvq2whFasAQAQEO6feIsqke5aL+RWPlELGhofoDXubb+Mp1B637kzBTlr+ErFwfXQaxBfwSMmwnZGQ==" saltValue="dKVGoja7LewvHvVElVMUkw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -38836,7 +38664,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>166</v>
       </c>
@@ -38860,7 +38688,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
         <v>339</v>
       </c>
@@ -38878,7 +38706,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>189</v>
       </c>
@@ -38902,7 +38730,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
         <v>339</v>
       </c>
@@ -38920,7 +38748,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -38944,7 +38772,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>339</v>
       </c>
@@ -38988,7 +38816,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>166</v>
       </c>
@@ -39015,7 +38843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
         <v>339</v>
       </c>
@@ -39032,7 +38860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>189</v>
       </c>
@@ -39059,7 +38887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
         <v>339</v>
       </c>
@@ -39080,7 +38908,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>188</v>
       </c>
@@ -39107,7 +38935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
         <v>339</v>
       </c>
@@ -39154,7 +38982,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>166</v>
       </c>
@@ -39181,7 +39009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C21" s="8" t="s">
         <v>339</v>
       </c>
@@ -39198,7 +39026,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>189</v>
       </c>
@@ -39225,7 +39053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="8" t="s">
         <v>339</v>
       </c>
@@ -39246,7 +39074,7 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>188</v>
       </c>
@@ -39273,7 +39101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>339</v>
       </c>
@@ -39295,7 +39123,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AEe4sFVFvJdxlxwYb5/Fb4/MP2c1Thmxs8d6Kg6mbyyF3A8vqdudF7AEakS5XTbz+0aw0cC50dYPq5OKJ5GjFA==" saltValue="/1EzdGwUMQRpbwulsInwqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="psnoTBwA1j35khW1cWNLM3Gc0jywv3Pl7+vW1fPCaAf9TjWgsd9Ef4ksYq8VldSMatse97qaQ4yEtVIXl9aPgA==" saltValue="OZMYwuEGqGmsYLMoguLVpw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39317,7 +39145,7 @@
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="str">
         <f>"Porcentaje de muertes en el año de referencia ("&amp;start_year&amp;") atribuible a la causa"</f>
-        <v>Porcentaje de muertes en el año de referencia (2021) atribuible a la causa</v>
+        <v>Porcentaje de muertes en el año de referencia (2024) atribuible a la causa</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -39353,7 +39181,7 @@
         <v>97</v>
       </c>
       <c r="C4" s="101">
-        <v>4.101989841625385E-2</v>
+        <v>4.0816004081600382E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39361,7 +39189,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="101">
-        <v>4.9011360386971133E-2</v>
+        <v>4.5121704512170478E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39369,7 +39197,7 @@
         <v>91</v>
       </c>
       <c r="C6" s="101">
-        <v>0.1588085734966799</v>
+        <v>0.16704491670449181</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39377,7 +39205,7 @@
         <v>96</v>
       </c>
       <c r="C7" s="101">
-        <v>0.46659760697486791</v>
+        <v>0.41512384151238468</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39393,7 +39221,7 @@
         <v>92</v>
       </c>
       <c r="C9" s="101">
-        <v>0.2429543801360107</v>
+        <v>0.28284702828470237</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39401,7 +39229,7 @@
         <v>94</v>
       </c>
       <c r="C10" s="101">
-        <v>4.1608180589216497E-2</v>
+        <v>4.9046504904650429E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39410,7 +39238,7 @@
       </c>
       <c r="C11" s="48">
         <f>SUM(C3:C10)</f>
-        <v>0.99999999999999989</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
@@ -39450,16 +39278,16 @@
         <v>84</v>
       </c>
       <c r="C14" s="55">
-        <v>3.5283536903939747E-2</v>
+        <v>7.1622213918380306E-2</v>
       </c>
       <c r="D14" s="55">
-        <v>3.5283536903939747E-2</v>
+        <v>7.1622213918380306E-2</v>
       </c>
       <c r="E14" s="55">
-        <v>3.5283536903939747E-2</v>
+        <v>7.1622213918380306E-2</v>
       </c>
       <c r="F14" s="55">
-        <v>3.5283536903939747E-2</v>
+        <v>7.1622213918380306E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39467,16 +39295,16 @@
         <v>102</v>
       </c>
       <c r="C15" s="101">
-        <v>0.23201731512421031</v>
+        <v>0.53537243852516658</v>
       </c>
       <c r="D15" s="101">
-        <v>0.23201731512421031</v>
+        <v>0.53537243852516658</v>
       </c>
       <c r="E15" s="101">
-        <v>0.23201731512421031</v>
+        <v>0.53537243852516658</v>
       </c>
       <c r="F15" s="101">
-        <v>0.23201731512421031</v>
+        <v>0.53537243852516658</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39484,16 +39312,16 @@
         <v>2</v>
       </c>
       <c r="C16" s="101">
-        <v>2.5289191581951111E-2</v>
+        <v>5.3815270817032607E-2</v>
       </c>
       <c r="D16" s="101">
-        <v>2.5289191581951111E-2</v>
+        <v>5.3815270817032607E-2</v>
       </c>
       <c r="E16" s="101">
-        <v>2.5289191581951111E-2</v>
+        <v>5.3815270817032607E-2</v>
       </c>
       <c r="F16" s="101">
-        <v>2.5289191581951111E-2</v>
+        <v>5.3815270817032607E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39552,16 +39380,16 @@
         <v>79</v>
       </c>
       <c r="C20" s="101">
-        <v>4.3314426319716942E-3</v>
+        <v>1.191361167876611E-2</v>
       </c>
       <c r="D20" s="101">
-        <v>4.3314426319716942E-3</v>
+        <v>1.191361167876611E-2</v>
       </c>
       <c r="E20" s="101">
-        <v>4.3314426319716942E-3</v>
+        <v>1.191361167876611E-2</v>
       </c>
       <c r="F20" s="101">
-        <v>4.3314426319716942E-3</v>
+        <v>1.191361167876611E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39569,16 +39397,16 @@
         <v>88</v>
       </c>
       <c r="C21" s="101">
-        <v>0.1123315245439216</v>
+        <v>0.25827184543585707</v>
       </c>
       <c r="D21" s="101">
-        <v>0.1123315245439216</v>
+        <v>0.25827184543585707</v>
       </c>
       <c r="E21" s="101">
-        <v>0.1123315245439216</v>
+        <v>0.25827184543585707</v>
       </c>
       <c r="F21" s="101">
-        <v>0.1123315245439216</v>
+        <v>0.25827184543585707</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39586,16 +39414,16 @@
         <v>99</v>
       </c>
       <c r="C22" s="101">
-        <v>0.59074698921400559</v>
+        <v>6.9004619624797536E-2</v>
       </c>
       <c r="D22" s="101">
-        <v>0.59074698921400559</v>
+        <v>6.9004619624797536E-2</v>
       </c>
       <c r="E22" s="101">
-        <v>0.59074698921400559</v>
+        <v>6.9004619624797536E-2</v>
       </c>
       <c r="F22" s="101">
-        <v>0.59074698921400559</v>
+        <v>6.9004619624797536E-2</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39604,19 +39432,19 @@
       </c>
       <c r="C23" s="48">
         <f>SUM(C14:C22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D23" s="48">
         <f>SUM(D14:D22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E23" s="48">
         <f>SUM(E14:E22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="F23" s="48">
         <f>SUM(F14:F22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -39728,7 +39556,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3yKJyuOHtg3sG34ZHEZfI+fd6GoHaBwt2IbVdjP6We9tBW/Mcrs4iY/0OZT1bu9crdkp1xq9Ow9FA1FxvpLazw==" saltValue="cQzosaHf/PLUT5hta6abgw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0mlqMf6g2pg1OU2sF4Guyln904xH64B8BJ04gN4fCOGkY/02N0RSrnb9xmyWkeAW79w5dpIlJrFdGjeTk5Qv3Q==" saltValue="Wr1ri1LwoCDsgKPLgXWMpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39750,7 +39578,7 @@
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Porcentaje de población en cada categoría en el año de referencia ("&amp;start_year&amp;")"</f>
-        <v>Porcentaje de población en cada categoría en el año de referencia (2021)</v>
+        <v>Porcentaje de población en cada categoría en el año de referencia (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
@@ -39780,23 +39608,23 @@
       </c>
       <c r="C2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.58437563457141883</v>
+        <v>0.58297288271154679</v>
       </c>
       <c r="D2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.58457492048436066</v>
+        <v>0.58297288271154679</v>
       </c>
       <c r="E2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.58246549792395419</v>
+        <v>0.58156996680665163</v>
       </c>
       <c r="F2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.50092793318511419</v>
+        <v>0.50195502496214828</v>
       </c>
       <c r="G2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.51589053854357536</v>
+        <v>0.51614479216839237</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39805,23 +39633,23 @@
       </c>
       <c r="C3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE) - SUM(C4:C5), "")</f>
-        <v>0.30307862771519101</v>
+        <v>0.30379262193961598</v>
       </c>
       <c r="D3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE) - SUM(D4:D5), "")</f>
-        <v>0.30297699132207184</v>
+        <v>0.30379262193961598</v>
       </c>
       <c r="E3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.30405026808033742</v>
+        <v>0.30450421923985999</v>
       </c>
       <c r="F3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.34097897876232264</v>
+        <v>0.34057260294482855</v>
       </c>
       <c r="G3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.33490285435371436</v>
+        <v>0.33479674271532855</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39829,19 +39657,19 @@
         <v>110</v>
       </c>
       <c r="C4" s="45">
-        <v>6.8506343215358007E-2</v>
+        <v>6.7813423255813993E-2</v>
       </c>
       <c r="D4" s="53">
-        <v>6.8506343215358007E-2</v>
+        <v>6.7813423255813993E-2</v>
       </c>
       <c r="E4" s="53">
-        <v>6.0878984057916898E-2</v>
+        <v>5.9689727906976797E-2</v>
       </c>
       <c r="F4" s="53">
-        <v>9.30039194557684E-2</v>
+        <v>9.1590816279069689E-2</v>
       </c>
       <c r="G4" s="53">
-        <v>9.5245285743845595E-2</v>
+        <v>9.4087655813953508E-2</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39849,19 +39677,19 @@
         <v>106</v>
       </c>
       <c r="C5" s="45">
-        <v>4.4039394498032201E-2</v>
+        <v>4.5421072093023297E-2</v>
       </c>
       <c r="D5" s="53">
-        <v>4.3941744978209497E-2</v>
+        <v>4.5421072093023297E-2</v>
       </c>
       <c r="E5" s="53">
-        <v>5.2605249937791497E-2</v>
+        <v>5.4236086046511603E-2</v>
       </c>
       <c r="F5" s="53">
-        <v>6.5089168596794797E-2</v>
+        <v>6.5881555813953496E-2</v>
       </c>
       <c r="G5" s="53">
-        <v>5.3961321358864688E-2</v>
+        <v>5.4970809302325598E-2</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39889,23 +39717,23 @@
       </c>
       <c r="C8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.57831498063356757</v>
+        <v>0.57723804055256789</v>
       </c>
       <c r="D8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.57831498063356757</v>
+        <v>0.57723804055256789</v>
       </c>
       <c r="E8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.7072874761722443</v>
+        <v>0.70781028816723035</v>
       </c>
       <c r="F8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.79100277724113255</v>
+        <v>0.79165112833288565</v>
       </c>
       <c r="G8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.80908093685773375</v>
+        <v>0.80972013337160054</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39914,23 +39742,23 @@
       </c>
       <c r="C9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE) - SUM(C10:C11), "")</f>
-        <v>0.30614564363728841</v>
+        <v>0.30668575944743215</v>
       </c>
       <c r="D9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE) - SUM(D10:D11), "")</f>
-        <v>0.30614564363728841</v>
+        <v>0.30668575944743215</v>
       </c>
       <c r="E9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE) - SUM(E10:E11), "")</f>
-        <v>0.23159713845068106</v>
+        <v>0.23125796764672316</v>
       </c>
       <c r="F9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE) - SUM(F10:F11), "")</f>
-        <v>0.17384200729234547</v>
+        <v>0.17336841352757945</v>
       </c>
       <c r="G9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE) - SUM(G10:G11), "")</f>
-        <v>0.16048929055437519</v>
+        <v>0.16001159686095753</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39938,19 +39766,19 @@
         <v>107</v>
       </c>
       <c r="C10" s="45">
-        <v>7.0007490607840603E-2</v>
+        <v>6.98490372093023E-2</v>
       </c>
       <c r="D10" s="53">
-        <v>7.0007490607840603E-2</v>
+        <v>6.98490372093023E-2</v>
       </c>
       <c r="E10" s="53">
-        <v>4.0488959954615197E-2</v>
+        <v>4.0427406976744198E-2</v>
       </c>
       <c r="F10" s="53">
-        <v>2.16110665718461E-2</v>
+        <v>2.1331202325581399E-2</v>
       </c>
       <c r="G10" s="53">
-        <v>1.8143644083632001E-2</v>
+        <v>1.7904416279069801E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39958,19 +39786,19 @@
         <v>119</v>
       </c>
       <c r="C11" s="45">
-        <v>4.5531885121303413E-2</v>
+        <v>4.6227162790697697E-2</v>
       </c>
       <c r="D11" s="53">
-        <v>4.5531885121303413E-2</v>
+        <v>4.6227162790697697E-2</v>
       </c>
       <c r="E11" s="53">
-        <v>2.0626425422459502E-2</v>
+        <v>2.0504337209302299E-2</v>
       </c>
       <c r="F11" s="53">
-        <v>1.35441488946759E-2</v>
+        <v>1.3649255813953501E-2</v>
       </c>
       <c r="G11" s="53">
-        <v>1.22861285042591E-2</v>
+        <v>1.2363853488372101E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -40147,7 +39975,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0rvqJJWwoexg1p6zocyuozzjPFkdqAA2IfWzpZetKCw+eW1d0Y3evTgk5WpmhkyR0Lvb034KeaiIy2Qe+zMA7Q==" saltValue="Laa9//zz0nHSF6OH6n36Ow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zqY6V+KCaMeLrzqb3kAjpBycNLHjJ5fYosVsK9ZcYca27jPFKQjHa0s9fQYdz5e3NZNR1nBMSOZibGy/tNIU8w==" saltValue="lSZUeq78QOJR3Wgj9wrK9g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40169,7 +39997,7 @@
     <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Porcentaje de niños en cada categoría en el año de referencia ("&amp;start_year&amp;")"</f>
-        <v>Porcentaje de niños en cada categoría en el año de referencia (2021)</v>
+        <v>Porcentaje de niños en cada categoría en el año de referencia (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
@@ -40198,64 +40026,78 @@
         <v>124</v>
       </c>
       <c r="C2" s="45">
-        <v>0.43501501852123098</v>
+        <v>0.43399436200000002</v>
       </c>
       <c r="D2" s="53">
-        <v>0.23498266272916701</v>
-      </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+        <v>0.23404619600000001</v>
+      </c>
+      <c r="E2" s="53">
+        <v>0</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="53">
-        <v>0.2763713716074</v>
+        <v>0.27557090400000001</v>
       </c>
       <c r="D3" s="53">
-        <v>0.288356971458333</v>
-      </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
+        <v>0.28600471399999999</v>
+      </c>
+      <c r="E3" s="53">
+        <v>0</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0</v>
+      </c>
+      <c r="G3" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="53">
-        <v>0.208402150173296</v>
+        <v>0.20970329800000001</v>
       </c>
       <c r="D4" s="53">
-        <v>0.32155992791666699</v>
+        <v>0.320885694</v>
       </c>
       <c r="E4" s="53">
-        <v>0.67901725684710901</v>
+        <v>0.65853112884615395</v>
       </c>
       <c r="F4" s="53">
-        <v>0.33638759210421898</v>
-      </c>
-      <c r="G4" s="53"/>
+        <v>0.32869853269230798</v>
+      </c>
+      <c r="G4" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C5" s="52">
-        <v>8.0177836077641909E-2</v>
+        <v>8.0731462000000004E-2</v>
       </c>
       <c r="D5" s="52">
-        <v>0.15519734193479201</v>
+        <v>0.15906339</v>
       </c>
       <c r="E5" s="52">
         <f>1-SUM(E2:E4)</f>
-        <v>0.32098274315289099</v>
+        <v>0.34146887115384605</v>
       </c>
       <c r="F5" s="52">
         <f>1-SUM(F2:F4)</f>
-        <v>0.66361240789578102</v>
+        <v>0.67130146730769202</v>
       </c>
       <c r="G5" s="52">
         <f>1-SUM(G2:G4)</f>
@@ -40263,7 +40105,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="euPG7p/BvoK8fNqiUHbVQntZxrTZDlcFWCFUSJiks61XnwHBR0ytGvXbGZpWhH6Q/fVHXMwBDzWb5XLP3KTOJQ==" saltValue="QPaCMchQWCq3fhuQ1/8qIQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rihKXJJWx+JcPnVDPlsVhDg2djhEMTm+etLiQzpCKrajI+gqu6w4SG8esf/c0BiU6PZb39QK/47TY71w6jHkRQ==" saltValue="yyL7dxMfiKo8AltpdAdUrw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40316,7 +40158,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -40333,10 +40175,10 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -40353,10 +40195,10 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -40373,7 +40215,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>104</v>
       </c>
@@ -40387,7 +40229,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>139</v>
       </c>
@@ -40401,7 +40243,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>134</v>
       </c>
@@ -40418,7 +40260,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>131</v>
       </c>
@@ -40432,7 +40274,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -40449,7 +40291,7 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>132</v>
       </c>
@@ -40464,7 +40306,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NMjQ3kAIwcLHVcRh8rPke05McY2SlAFLK7Ah1UqrRYQ2CBpairZvwUjXH6x9P1jYAZpBvNqGehS4h5QZ+R1R7w==" saltValue="3sonNQo8H1uukN9Ne6Lfxg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XgFg0Ad0lLNdfXKCweqEeu0R1wTG1kDX8EsiY7+cYsVlzn2IVKkMyT0ZzVoeUvxQ2jVkjQlDBkuyPZgro0qUQQ==" saltValue="n622QzzR91pV+ZkQYU2SCg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -40490,7 +40332,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>144</v>
       </c>
@@ -40498,7 +40340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>143</v>
       </c>
@@ -40506,7 +40348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>142</v>
       </c>
@@ -40514,7 +40356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>146</v>
       </c>
@@ -40522,7 +40364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>140</v>
       </c>
@@ -40530,7 +40372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>141</v>
       </c>
@@ -40539,7 +40381,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vbZ6M0tgbTTEJCh7b8DUWKNE5hvUerqYOXQxGQ+GmxkeoTFOKRZzraQGQRWb8LSC/0YKZ2Gjoh4xnqz6R8yaGQ==" saltValue="Dh0MmSUBSnmMBj6ecvRYSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rRYhFEa2yGN2v2Jpzz19lkt277uILA4DCooUlCKfQDJqIjobUDGIlyqm0QYHfEhHdMeDXjs8GGdHsYo2CzCsUw==" saltValue="qWMAYIPlvELfsIH7/F7PRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40591,7 +40433,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>78</v>
       </c>
@@ -40604,7 +40446,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>74</v>
       </c>
@@ -40617,29 +40459,33 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>77</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E5" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>75</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E6" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
         <v>148</v>
       </c>
@@ -40661,7 +40507,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>78</v>
       </c>
@@ -40672,7 +40518,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>74</v>
       </c>
@@ -40683,7 +40529,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="32" t="s">
         <v>77</v>
       </c>
@@ -40696,7 +40542,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="32" t="s">
         <v>75</v>
       </c>
@@ -40709,7 +40555,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
         <v>148</v>
       </c>
@@ -40733,7 +40579,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
         <v>78</v>
       </c>
@@ -40746,7 +40592,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>74</v>
       </c>
@@ -40759,7 +40605,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
         <v>77</v>
       </c>
@@ -40772,7 +40618,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="32" t="s">
         <v>75</v>
       </c>
@@ -40785,7 +40631,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
         <v>148</v>
       </c>
@@ -40794,7 +40640,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jH9lBml99HhjI1VOr8blM0tWKmL8m324zkpk7c3FS8ADw1fmpuIP2JgUcp1DKfK85dEeJDbXpQmNolOlK3kt3A==" saltValue="n138ekJEThvQRKjq5ghGCw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vPW6KByrkdWc/Ur/G4FYQG5C/EPQj5IM/c57WkUvFCd3qwWt6aaPvFjUK4FgAibHm12bFjqMpUBp7BS+66T9UA==" saltValue="QEZEsSbG75uZSPruB5aoyA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -40853,7 +40699,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zE4Rw4JZirJh2YIR6zyrVIonHgfMt7QSJu4ueMKyam+M0zSdzFzlbfrkxgWzjMTby7FpgzN0E70cZfjcyfME4Q==" saltValue="hvCdCj6TrrkgM+wOF1qaWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ft7LKEaGesjW8zRyZbm0NM9/I2P7tehwmDs/akNYuvnOpHlsEmjcVOM4ri9L4+3siTLuDdAn/B7Af723rrh+Bg==" saltValue="jg7V3KMzE2CmV4KE9kg4lQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>